--- a/TestWriteInExel/ExcelDataGmailData.xlsx
+++ b/TestWriteInExel/ExcelDataGmailData.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>Tài khoản</t>
   </si>
@@ -348,6 +348,15 @@
   </si>
   <si>
     <t>nu3o 276q kc5h hpjg fr3k g7aw guhw kvfl</t>
+  </si>
+  <si>
+    <t>donna90garrick1@gmail.com</t>
+  </si>
+  <si>
+    <t>SKNHI6nHdldR</t>
+  </si>
+  <si>
+    <t>kslr dnos 7kii muaf r2o2 hgar ckbl kaje</t>
   </si>
 </sst>
 </file>
@@ -704,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.5546875" style="1" customWidth="1"/>
@@ -1106,6 +1115,17 @@
       </c>
       <c r="C36" s="1" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/TestWriteInExel/ExcelDataGmailData.xlsx
+++ b/TestWriteInExel/ExcelDataGmailData.xlsx
@@ -373,6 +373,12 @@
   </x:si>
   <x:si>
     <x:t>HLBG@jMJ7XfF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>luccy87fergal1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>s%qb2y&amp;1&amp;flt</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1184,14 +1190,22 @@
         <x:v>115</x:v>
       </x:c>
     </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="A2" r:id="rId14"/>
-    <x:hyperlink ref="A7" r:id="rId15"/>
-    <x:hyperlink ref="A6" r:id="rId16"/>
-    <x:hyperlink ref="A8" r:id="rId17"/>
-    <x:hyperlink ref="A22" r:id="rId18"/>
-    <x:hyperlink ref="A38" r:id="rId19"/>
+    <x:hyperlink ref="A2" r:id="rId12"/>
+    <x:hyperlink ref="A7" r:id="rId13"/>
+    <x:hyperlink ref="A6" r:id="rId20"/>
+    <x:hyperlink ref="A8" r:id="rId21"/>
+    <x:hyperlink ref="A22" r:id="rId22"/>
+    <x:hyperlink ref="A38" r:id="rId23"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TestWriteInExel/ExcelDataGmailData.xlsx
+++ b/TestWriteInExel/ExcelDataGmailData.xlsx
@@ -379,6 +379,12 @@
   </x:si>
   <x:si>
     <x:t>s%qb2y&amp;1&amp;flt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>donna63cadell1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>^&amp;3DGXm&amp;NUaw</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1198,14 +1204,22 @@
         <x:v>117</x:v>
       </x:c>
     </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="A2" r:id="rId12"/>
-    <x:hyperlink ref="A7" r:id="rId13"/>
-    <x:hyperlink ref="A6" r:id="rId20"/>
-    <x:hyperlink ref="A8" r:id="rId21"/>
-    <x:hyperlink ref="A22" r:id="rId22"/>
-    <x:hyperlink ref="A38" r:id="rId23"/>
+    <x:hyperlink ref="A2" r:id="rId14"/>
+    <x:hyperlink ref="A7" r:id="rId15"/>
+    <x:hyperlink ref="A6" r:id="rId16"/>
+    <x:hyperlink ref="A8" r:id="rId17"/>
+    <x:hyperlink ref="A22" r:id="rId18"/>
+    <x:hyperlink ref="A38" r:id="rId19"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
